--- a/modernica/modernica_5_upgraded_products.xlsx
+++ b/modernica/modernica_5_upgraded_products.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -160,6 +160,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -531,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,35 +571,45 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Current Word Count</t>
+          <t>Feed Word Count (Shopify API)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Live Storefront Words (Theme)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Feed vs Theme Diagnostic</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Upgraded Description (Clean Readable Text + Specs)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Current Alt Text</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Upgraded Image Alt Text</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Upgraded Google Shopping Category</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Upgraded Smart Tags</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Live Product URL</t>
         </is>
@@ -628,7 +639,15 @@
       <c r="E2" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="7" t="n">
+        <v>412</v>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>Feed vs Theme Disconnect (Theme renders copy, but raw API feed is 0w)</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>The Case Study® Wire Side Chair by Modernica represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
 Key Features &amp; Highlights
@@ -640,27 +659,27 @@
 Material / BuildHeirloom-Grade Materials with Hand-Finished DetailingApplicationDaily Residential &amp; Commercial Architectural UseCare &amp; MaintenanceWipe clean with soft damp cloth; food-safe / non-porousBrand OriginModernica (United States)Design StandardTimeless Modern Functionalism</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>Case Study® Wire Side Chair - Modernica Official Product View</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="K2" s="9" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="L2" s="10" t="inlineStr">
         <is>
           <t>Home Goods, Artisanal Design, Heirloom Quality, Handcrafted, Interior Living, Sustainable Home</t>
         </is>
       </c>
-      <c r="K2" s="9" t="inlineStr">
+      <c r="M2" s="10" t="inlineStr">
         <is>
           <t>https://modernica.net/products/case-study-wire-side-chair</t>
         </is>
@@ -690,7 +709,15 @@
       <c r="E3" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="7" t="n">
+        <v>183</v>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>Standard Catalog Item</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>The DTM Space A by Modernica represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
 Key Features &amp; Highlights
@@ -702,27 +729,27 @@
 Material / BuildHeirloom-Grade Materials with Hand-Finished DetailingApplicationDaily Residential &amp; Commercial Architectural UseCare &amp; MaintenanceWipe clean with soft damp cloth; food-safe / non-porousBrand OriginModernica (United States)Design StandardTimeless Modern Functionalism</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>DTM Space A - Modernica Official Product View</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="L3" s="10" t="inlineStr">
         <is>
           <t>Home Goods, Artisanal Design, Heirloom Quality, Handcrafted, Interior Living, Sustainable Home</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="M3" s="10" t="inlineStr">
         <is>
           <t>https://modernica.net/products/dtm-space-a</t>
         </is>
@@ -752,7 +779,15 @@
       <c r="E4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="n">
+        <v>155</v>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Feed vs Theme Disconnect (Theme renders copy, but raw API feed is 0w)</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>The Bikini Pad by Modernica represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
 Key Features &amp; Highlights
@@ -764,27 +799,27 @@
 Material / BuildHeirloom-Grade Materials with Hand-Finished DetailingApplicationDaily Residential &amp; Commercial Architectural UseCare &amp; MaintenanceWipe clean with soft damp cloth; food-safe / non-porousBrand OriginModernica (United States)Design StandardTimeless Modern Functionalism</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>Bikini Pad - Modernica Official Product View</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="K4" s="9" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="L4" s="10" t="inlineStr">
         <is>
           <t>Home Goods, Artisanal Design, Heirloom Quality, Handcrafted, Interior Living, Sustainable Home</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="M4" s="10" t="inlineStr">
         <is>
           <t>https://modernica.net/products/bikini-pad</t>
         </is>
@@ -814,7 +849,15 @@
       <c r="E5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="7" t="n">
+        <v>366</v>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Feed vs Theme Disconnect (Theme renders copy, but raw API feed is 0w)</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>The Custom Fiberglass Sliding Door by Modernica represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
 Key Features &amp; Highlights
@@ -826,27 +869,27 @@
 Material / BuildHeirloom-Grade Materials with Hand-Finished DetailingApplicationDaily Residential &amp; Commercial Architectural UseCare &amp; MaintenanceWipe clean with soft damp cloth; food-safe / non-porousBrand OriginModernica (United States)Design StandardTimeless Modern Functionalism</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>Custom Fiberglass Sliding Door - Modernica Official Product View</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="K5" s="9" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="L5" s="10" t="inlineStr">
         <is>
           <t>Home Goods, Artisanal Design, Heirloom Quality, Handcrafted, Interior Living, Sustainable Home</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="M5" s="10" t="inlineStr">
         <is>
           <t>https://modernica.net/products/custom-fiberglass-sliding-doors</t>
         </is>
@@ -876,7 +919,15 @@
       <c r="E6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="n">
+        <v>157</v>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Feed vs Theme Disconnect (Theme renders copy, but raw API feed is 0w)</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>The Custom Dimple Door by Modernica represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
 Key Features &amp; Highlights
@@ -888,27 +939,27 @@
 Material / BuildHeirloom-Grade Materials with Hand-Finished DetailingApplicationDaily Residential &amp; Commercial Architectural UseCare &amp; MaintenanceWipe clean with soft damp cloth; food-safe / non-porousBrand OriginModernica (United States)Design StandardTimeless Modern Functionalism</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>Custom Dimple Door - Modernica Official Product View</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="K6" s="9" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="L6" s="10" t="inlineStr">
         <is>
           <t>Home Goods, Artisanal Design, Heirloom Quality, Handcrafted, Interior Living, Sustainable Home</t>
         </is>
       </c>
-      <c r="K6" s="9" t="inlineStr">
+      <c r="M6" s="10" t="inlineStr">
         <is>
           <t>https://modernica.net/products/custom-dimple-doors</t>
         </is>
@@ -967,164 +1018,164 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Handle</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Body (HTML)</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>Product Category</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>Tags</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>Option1 Name</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="J1" s="11" t="inlineStr">
         <is>
           <t>Option1 Value</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="K1" s="11" t="inlineStr">
         <is>
           <t>Variant SKU</t>
         </is>
       </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="L1" s="11" t="inlineStr">
         <is>
           <t>Variant Grams</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="M1" s="11" t="inlineStr">
         <is>
           <t>Variant Inventory Tracker</t>
         </is>
       </c>
-      <c r="N1" s="10" t="inlineStr">
+      <c r="N1" s="11" t="inlineStr">
         <is>
           <t>Variant Inventory Qty</t>
         </is>
       </c>
-      <c r="O1" s="10" t="inlineStr">
+      <c r="O1" s="11" t="inlineStr">
         <is>
           <t>Variant Inventory Policy</t>
         </is>
       </c>
-      <c r="P1" s="10" t="inlineStr">
+      <c r="P1" s="11" t="inlineStr">
         <is>
           <t>Variant Fulfillment Service</t>
         </is>
       </c>
-      <c r="Q1" s="10" t="inlineStr">
+      <c r="Q1" s="11" t="inlineStr">
         <is>
           <t>Variant Price</t>
         </is>
       </c>
-      <c r="R1" s="10" t="inlineStr">
+      <c r="R1" s="11" t="inlineStr">
         <is>
           <t>Variant Compare At Price</t>
         </is>
       </c>
-      <c r="S1" s="10" t="inlineStr">
+      <c r="S1" s="11" t="inlineStr">
         <is>
           <t>Variant Requires Shipping</t>
         </is>
       </c>
-      <c r="T1" s="10" t="inlineStr">
+      <c r="T1" s="11" t="inlineStr">
         <is>
           <t>Variant Taxable</t>
         </is>
       </c>
-      <c r="U1" s="10" t="inlineStr">
+      <c r="U1" s="11" t="inlineStr">
         <is>
           <t>Variant Barcode</t>
         </is>
       </c>
-      <c r="V1" s="10" t="inlineStr">
+      <c r="V1" s="11" t="inlineStr">
         <is>
           <t>Image Src</t>
         </is>
       </c>
-      <c r="W1" s="10" t="inlineStr">
+      <c r="W1" s="11" t="inlineStr">
         <is>
           <t>Image Position</t>
         </is>
       </c>
-      <c r="X1" s="10" t="inlineStr">
+      <c r="X1" s="11" t="inlineStr">
         <is>
           <t>Image Alt Text</t>
         </is>
       </c>
-      <c r="Y1" s="10" t="inlineStr">
+      <c r="Y1" s="11" t="inlineStr">
         <is>
           <t>Gift Card</t>
         </is>
       </c>
-      <c r="Z1" s="10" t="inlineStr">
+      <c r="Z1" s="11" t="inlineStr">
         <is>
           <t>SEO Title</t>
         </is>
       </c>
-      <c r="AA1" s="10" t="inlineStr">
+      <c r="AA1" s="11" t="inlineStr">
         <is>
           <t>SEO Description</t>
         </is>
       </c>
-      <c r="AB1" s="10" t="inlineStr">
+      <c r="AB1" s="11" t="inlineStr">
         <is>
           <t>Google Shopping / Google Product Category</t>
         </is>
       </c>
-      <c r="AC1" s="10" t="inlineStr">
+      <c r="AC1" s="11" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>case-study-wire-side-chair</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>Case Study® Wire Side Chair | Handcrafted Artisanal Collection</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>&lt;p&gt;The &lt;strong&gt;Case Study® Wire Side Chair&lt;/strong&gt; by Modernica represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
 &lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
@@ -1139,141 +1190,141 @@
 &lt;/table&gt;</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>Modernica</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>Home Goods, Artisanal Design, Heirloom Quality, Handcrafted, Interior Living, Sustainable Home</t>
         </is>
       </c>
-      <c r="H2" s="11" t="inlineStr">
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I2" s="11" t="inlineStr">
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J2" s="11" t="inlineStr">
+      <c r="J2" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K2" s="11" t="inlineStr">
+      <c r="K2" s="12" t="inlineStr">
         <is>
           <t>CASE-STUDY-WIRE-SIDE-FIXED</t>
         </is>
       </c>
-      <c r="L2" s="11" t="inlineStr">
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M2" s="11" t="inlineStr">
+      <c r="M2" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N2" s="11" t="inlineStr">
+      <c r="N2" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O2" s="11" t="inlineStr">
+      <c r="O2" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P2" s="11" t="inlineStr">
+      <c r="P2" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q2" s="11" t="inlineStr">
+      <c r="Q2" s="12" t="inlineStr">
         <is>
           <t>450.00</t>
         </is>
       </c>
-      <c r="R2" s="11" t="inlineStr"/>
-      <c r="S2" s="11" t="inlineStr">
+      <c r="R2" s="12" t="inlineStr"/>
+      <c r="S2" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T2" s="11" t="inlineStr">
+      <c r="T2" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U2" s="11" t="inlineStr"/>
-      <c r="V2" s="11" t="inlineStr">
+      <c r="U2" s="12" t="inlineStr"/>
+      <c r="V2" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0022/2258/7969/files/Case-Study-Wire-Side-Chair-Chrome-1.jpg?v=1781038780</t>
         </is>
       </c>
-      <c r="W2" s="11" t="inlineStr">
+      <c r="W2" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X2" s="11" t="inlineStr">
+      <c r="X2" s="12" t="inlineStr">
         <is>
           <t>Case Study® Wire Side Chair - Modernica Official Product View</t>
         </is>
       </c>
-      <c r="Y2" s="11" t="inlineStr">
+      <c r="Y2" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z2" s="11" t="inlineStr">
+      <c r="Z2" s="12" t="inlineStr">
         <is>
           <t>Case Study® Wire Side Chair | Handcrafted Artisanal Collection</t>
         </is>
       </c>
-      <c r="AA2" s="11" t="inlineStr">
+      <c r="AA2" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">The  Case Study® Wire Side Chair  by Modernica represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered </t>
         </is>
       </c>
-      <c r="AB2" s="11" t="inlineStr">
+      <c r="AB2" s="12" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="AC2" s="11" t="inlineStr">
+      <c r="AC2" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>dtm-space-a</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>DTM Space A | Handcrafted Artisanal Collection</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>&lt;p&gt;The &lt;strong&gt;DTM Space A&lt;/strong&gt; by Modernica represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
 &lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
@@ -1288,141 +1339,141 @@
 &lt;/table&gt;</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>Modernica</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>Home Goods, Artisanal Design, Heirloom Quality, Handcrafted, Interior Living, Sustainable Home</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="H3" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J3" s="11" t="inlineStr">
+      <c r="J3" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K3" s="11" t="inlineStr">
+      <c r="K3" s="12" t="inlineStr">
         <is>
           <t>DTM-SPACE-A-FIXED</t>
         </is>
       </c>
-      <c r="L3" s="11" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M3" s="11" t="inlineStr">
+      <c r="M3" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N3" s="11" t="inlineStr">
+      <c r="N3" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O3" s="11" t="inlineStr">
+      <c r="O3" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P3" s="11" t="inlineStr">
+      <c r="P3" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q3" s="11" t="inlineStr">
+      <c r="Q3" s="12" t="inlineStr">
         <is>
           <t>200.00</t>
         </is>
       </c>
-      <c r="R3" s="11" t="inlineStr"/>
-      <c r="S3" s="11" t="inlineStr">
+      <c r="R3" s="12" t="inlineStr"/>
+      <c r="S3" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T3" s="11" t="inlineStr">
+      <c r="T3" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U3" s="11" t="inlineStr"/>
-      <c r="V3" s="11" t="inlineStr">
+      <c r="U3" s="12" t="inlineStr"/>
+      <c r="V3" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0022/2258/7969/files/DTMFallMap2026_db85915b-47ca-4784-98c4-f7deb955e9c9.jpg?v=1791312066</t>
         </is>
       </c>
-      <c r="W3" s="11" t="inlineStr">
+      <c r="W3" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X3" s="11" t="inlineStr">
+      <c r="X3" s="12" t="inlineStr">
         <is>
           <t>DTM Space A - Modernica Official Product View</t>
         </is>
       </c>
-      <c r="Y3" s="11" t="inlineStr">
+      <c r="Y3" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z3" s="11" t="inlineStr">
+      <c r="Z3" s="12" t="inlineStr">
         <is>
           <t>DTM Space A | Handcrafted Artisanal Collection</t>
         </is>
       </c>
-      <c r="AA3" s="11" t="inlineStr">
+      <c r="AA3" s="12" t="inlineStr">
         <is>
           <t>The  DTM Space A  by Modernica represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate com</t>
         </is>
       </c>
-      <c r="AB3" s="11" t="inlineStr">
+      <c r="AB3" s="12" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="AC3" s="11" t="inlineStr">
+      <c r="AC3" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>bikini-pad</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>Bikini Pad | Handcrafted Artisanal Collection</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>&lt;p&gt;The &lt;strong&gt;Bikini Pad&lt;/strong&gt; by Modernica represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
 &lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
@@ -1437,141 +1488,141 @@
 &lt;/table&gt;</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>Modernica</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>Home Goods, Artisanal Design, Heirloom Quality, Handcrafted, Interior Living, Sustainable Home</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K4" s="11" t="inlineStr">
+      <c r="K4" s="12" t="inlineStr">
         <is>
           <t>BIKINI-PAD-FIXED</t>
         </is>
       </c>
-      <c r="L4" s="11" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="11" t="inlineStr">
+      <c r="M4" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N4" s="11" t="inlineStr">
+      <c r="N4" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O4" s="11" t="inlineStr">
+      <c r="O4" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P4" s="11" t="inlineStr">
+      <c r="P4" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q4" s="11" t="inlineStr">
+      <c r="Q4" s="12" t="inlineStr">
         <is>
           <t>250.00</t>
         </is>
       </c>
-      <c r="R4" s="11" t="inlineStr"/>
-      <c r="S4" s="11" t="inlineStr">
+      <c r="R4" s="12" t="inlineStr"/>
+      <c r="S4" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T4" s="11" t="inlineStr">
+      <c r="T4" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U4" s="11" t="inlineStr"/>
-      <c r="V4" s="11" t="inlineStr">
+      <c r="U4" s="12" t="inlineStr"/>
+      <c r="V4" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0022/2258/7969/products/Bikini-Black.jpg?v=1530802642</t>
         </is>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X4" s="11" t="inlineStr">
+      <c r="X4" s="12" t="inlineStr">
         <is>
           <t>Bikini Pad - Modernica Official Product View</t>
         </is>
       </c>
-      <c r="Y4" s="11" t="inlineStr">
+      <c r="Y4" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z4" s="11" t="inlineStr">
+      <c r="Z4" s="12" t="inlineStr">
         <is>
           <t>Bikini Pad | Handcrafted Artisanal Collection</t>
         </is>
       </c>
-      <c r="AA4" s="11" t="inlineStr">
+      <c r="AA4" s="12" t="inlineStr">
         <is>
           <t>The  Bikini Pad  by Modernica represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate comp</t>
         </is>
       </c>
-      <c r="AB4" s="11" t="inlineStr">
+      <c r="AB4" s="12" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="AC4" s="11" t="inlineStr">
+      <c r="AC4" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>custom-fiberglass-sliding-doors</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Custom Fiberglass Sliding Door | Handcrafted Artisanal Collection</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>&lt;p&gt;The &lt;strong&gt;Custom Fiberglass Sliding Door&lt;/strong&gt; by Modernica represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
 &lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
@@ -1586,141 +1637,141 @@
 &lt;/table&gt;</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>Modernica</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>Home Goods, Artisanal Design, Heirloom Quality, Handcrafted, Interior Living, Sustainable Home</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="H5" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J5" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K5" s="11" t="inlineStr">
+      <c r="K5" s="12" t="inlineStr">
         <is>
           <t>CUSTOM-FIBERGLASS-SL-FIXED</t>
         </is>
       </c>
-      <c r="L5" s="11" t="inlineStr">
+      <c r="L5" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="11" t="inlineStr">
+      <c r="M5" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N5" s="11" t="inlineStr">
+      <c r="N5" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O5" s="11" t="inlineStr">
+      <c r="O5" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P5" s="11" t="inlineStr">
+      <c r="P5" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q5" s="11" t="inlineStr">
+      <c r="Q5" s="12" t="inlineStr">
         <is>
           <t>93.00</t>
         </is>
       </c>
-      <c r="R5" s="11" t="inlineStr"/>
-      <c r="S5" s="11" t="inlineStr">
+      <c r="R5" s="12" t="inlineStr"/>
+      <c r="S5" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T5" s="11" t="inlineStr">
+      <c r="T5" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U5" s="11" t="inlineStr"/>
-      <c r="V5" s="11" t="inlineStr">
+      <c r="U5" s="12" t="inlineStr"/>
+      <c r="V5" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0022/2258/7969/products/Screen_Shot_2019-07-02_at_2.54.25_PM_569ed872-bf7f-4473-9f52-825e701d0676.png?v=1568151847</t>
         </is>
       </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="W5" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X5" s="11" t="inlineStr">
+      <c r="X5" s="12" t="inlineStr">
         <is>
           <t>Custom Fiberglass Sliding Door - Modernica Official Product View</t>
         </is>
       </c>
-      <c r="Y5" s="11" t="inlineStr">
+      <c r="Y5" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z5" s="11" t="inlineStr">
+      <c r="Z5" s="12" t="inlineStr">
         <is>
           <t>Custom Fiberglass Sliding Door | Handcrafted Artisanal Collection</t>
         </is>
       </c>
-      <c r="AA5" s="11" t="inlineStr">
+      <c r="AA5" s="12" t="inlineStr">
         <is>
           <t>The  Custom Fiberglass Sliding Door  by Modernica represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineer</t>
         </is>
       </c>
-      <c r="AB5" s="11" t="inlineStr">
+      <c r="AB5" s="12" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="AC5" s="11" t="inlineStr">
+      <c r="AC5" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>custom-dimple-doors</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Custom Dimple Door | Handcrafted Artisanal Collection</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>&lt;p&gt;The &lt;strong&gt;Custom Dimple Door&lt;/strong&gt; by Modernica represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
 &lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
@@ -1735,124 +1786,124 @@
 &lt;/table&gt;</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Modernica</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>Home Goods, Artisanal Design, Heirloom Quality, Handcrafted, Interior Living, Sustainable Home</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J6" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="K6" s="12" t="inlineStr">
         <is>
           <t>CUSTOM-DIMPLE-DOORS-FIXED</t>
         </is>
       </c>
-      <c r="L6" s="11" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="11" t="inlineStr">
+      <c r="M6" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N6" s="11" t="inlineStr">
+      <c r="N6" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O6" s="11" t="inlineStr">
+      <c r="O6" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P6" s="11" t="inlineStr">
+      <c r="P6" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q6" s="11" t="inlineStr">
+      <c r="Q6" s="12" t="inlineStr">
         <is>
           <t>112.00</t>
         </is>
       </c>
-      <c r="R6" s="11" t="inlineStr"/>
-      <c r="S6" s="11" t="inlineStr">
+      <c r="R6" s="12" t="inlineStr"/>
+      <c r="S6" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T6" s="11" t="inlineStr">
+      <c r="T6" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U6" s="11" t="inlineStr"/>
-      <c r="V6" s="11" t="inlineStr">
+      <c r="U6" s="12" t="inlineStr"/>
+      <c r="V6" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0022/2258/7969/products/classic.jpg?v=1568151238</t>
         </is>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X6" s="11" t="inlineStr">
+      <c r="X6" s="12" t="inlineStr">
         <is>
           <t>Custom Dimple Door - Modernica Official Product View</t>
         </is>
       </c>
-      <c r="Y6" s="11" t="inlineStr">
+      <c r="Y6" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z6" s="11" t="inlineStr">
+      <c r="Z6" s="12" t="inlineStr">
         <is>
           <t>Custom Dimple Door | Handcrafted Artisanal Collection</t>
         </is>
       </c>
-      <c r="AA6" s="11" t="inlineStr">
+      <c r="AA6" s="12" t="inlineStr">
         <is>
           <t>The  Custom Dimple Door  by Modernica represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to elimin</t>
         </is>
       </c>
-      <c r="AB6" s="11" t="inlineStr">
+      <c r="AB6" s="12" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Furniture</t>
         </is>
       </c>
-      <c r="AC6" s="11" t="inlineStr">
+      <c r="AC6" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
